--- a/ddl/2팀_요구사항명세서_v2.xlsx
+++ b/ddl/2팀_요구사항명세서_v2.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3774,146 +3774,47 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>SHP-06</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>출하</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>Document Service</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>FE</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>지연 상태/메모 업데이트 폼</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>[출하 담당자] 
-- 지연 상태(정상/지연 위험/지연)를 변경하거나, 지연 사유/메모를 입력할 수 있는 모달에서 저장한다. 
-[시스템] 
-- 저장 시 최근 업데이트 시각을 갱신한다.</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>강성훈</t>
-        </is>
-      </c>
-      <c r="I67" s="18" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  영업현황</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="15" t="n"/>
+      <c r="D67" s="15" t="n"/>
+      <c r="E67" s="15" t="n"/>
+      <c r="F67" s="15" t="n"/>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="16" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>SHP-07</t>
+          <t>SAL-01</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>출하</t>
+          <t>대시보드</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Document Service</t>
+          <t>Activity Service</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>지연 상태/메모 저장 API</t>
+          <t>매출/수금 대시보드</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>[시스템]
-- 지연 상태 및 지연 사유/메모를 저장한다.
-- 지연 상태 값의 유효성을 검증하고, 저장 시 최근 업데이트 시각을 갱신한다.</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>강성훈</t>
-        </is>
-      </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  영업현황</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
-      <c r="H69" s="15" t="n"/>
-      <c r="I69" s="16" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>SAL-01</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>FE</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>매출/수금 대시보드</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - 대시보드 화면에서 총 매출·총 수금·미수금·거래처 수 요약 카드를 확인한다.
@@ -3925,97 +3826,97 @@
 - 대시보드와 판매현황 페이지를 분리.</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>SAL-02</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>수금 현황 집계 API</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>[시스템]
 - 월별·거래처별 매출 및 수금 현황을 집계하고, 미수금 금액을 계산하여 반환한다.</t>
         </is>
       </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="G69" s="10" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>SAL-03</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>수금</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>수금 등록 화면</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - 수금 등록 화면에서 기존 수금 이력을 확인하고 새로운 수금 금액을 입력한 후 등록 버튼을 클릭한다.
@@ -4023,58 +3924,154 @@
 - 등록 후 잔액을 화면에 즉시 반영한다.</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I72" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>SAL-04</t>
         </is>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>수금</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E73" s="11" t="inlineStr">
+      <c r="E71" s="11" t="inlineStr">
         <is>
           <t>수금 등록/잔액 계산 API</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>[시스템]
 - 수금 내역을 저장하고 미수금 잔액을 자동 재계산한다.
 - 수금 상태(미수/부분수금/완납/연체)를 갱신한다.</t>
         </is>
       </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>강성훈</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>SAL-05</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>수금</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Activity Service</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>수금 이력 조회</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>[영업 담당자 / 관리자]
+- 거래건별 수금 이력 목록을 조회하고 총액·수금액·잔액 요약을 확인한다.</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>강성훈</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>SAL-06</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>수금</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Activity Service</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>수금 이력 조회 API</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>[시스템]
+- 수금 이력과 요약 정보를 조회하여 반환한다.</t>
+        </is>
+      </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -4091,12 +4088,12 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>SAL-05</t>
+          <t>SAL-07</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>수금</t>
+          <t>판매현황</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4111,106 +4108,10 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>수금 이력 조회</t>
+          <t>판매현황 통합 페이지</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>[영업 담당자 / 관리자]
-- 거래건별 수금 이력 목록을 조회하고 총액·수금액·잔액 요약을 확인한다.</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>강성훈</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>SAL-06</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>수금</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>수금 이력 조회 API</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>[시스템]
-- 수금 이력과 요약 정보를 조회하여 반환한다.</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>강성훈</t>
-        </is>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>SAL-07</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>판매현황</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>FE</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>판매현황 통합 페이지</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자]
 - 판매현황 페이지(/sales)에서 거래처, 담당 영업, 기간(시작/종료) 조건으로 데이터를 조회한다.
@@ -4222,49 +4123,49 @@
 - 초기화 버튼 클릭 시 조회 조건을 기본값으로 되돌린다.</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I76" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>SAL-08</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>수금</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E77" s="11" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>수금 관리 전용 페이지</t>
         </is>
       </c>
-      <c r="F77" s="12" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자]
 - 수금 관리(/collections) 페이지에서 '수금 관리' 탭(목록)과 '수금 등록' 탭을 전환할 수 있다.
@@ -4273,64 +4174,64 @@
 - 거래처 선택 시 해당 거래처에 매핑된 수금코드와 PO 번호만 조회할 수 있도록 한다.</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I77" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  맥락관리</t>
         </is>
       </c>
-      <c r="B78" s="15" t="n"/>
-      <c r="C78" s="15" t="n"/>
-      <c r="D78" s="15" t="n"/>
-      <c r="E78" s="15" t="n"/>
-      <c r="F78" s="15" t="n"/>
-      <c r="G78" s="15" t="n"/>
-      <c r="H78" s="15" t="n"/>
-      <c r="I78" s="16" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="15" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="15" t="n"/>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>CTX-01</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>정보페이지</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>거래처별 정보 페이지(허브 UI)</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - URL 직접 접근(#/client-hub) 또는 거래처 관리에서 진입하여, 해당 거래처의 정보 허브 페이지를 열 수 있다.
@@ -4343,49 +4244,49 @@
 - 사이드바 메뉴에는 미노출(라우트는 존재).</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>CTX-02</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>정보페이지</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>거래처 타임라인 조회 API</t>
         </is>
       </c>
-      <c r="F80" s="12" t="inlineStr">
+      <c r="F78" s="12" t="inlineStr">
         <is>
           <t>[시스템]
 - 거래처의 활동 기록을 시간 순서로 조회한다.
@@ -4393,49 +4294,49 @@
 - 페이징 조회를 지원한다.</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>CTX-03</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>이슈/코멘트/회의록 등록</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - 이슈·코멘트·회의록 등 활동 유형을 선택하고 내용을 작성한 후 등록 버튼을 클릭한다. 
@@ -4443,97 +4344,97 @@
 - 등록된 내용을 타임라인에 즉시 반영한다.</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>CTX-04</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>협업 기록 저장 API</t>
         </is>
       </c>
-      <c r="F82" s="12" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
         <is>
           <t>[시스템]
 - 사용자가 입력한 협업 기록(이슈·코멘트·회의록 등)을 저장한다.</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>CTX-05</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>이슈 상태/우선순위 관리</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - 이슈 항목에서 처리 상태(완료/미완료) 또는 우선순위를 변경한다.
@@ -4541,195 +4442,97 @@
 - 변경 결과를 즉시 화면에 반영한다.</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I83" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>CTX-06</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>이슈 상태/우선순위 변경 API</t>
         </is>
       </c>
-      <c r="F84" s="12" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>[시스템]
 - 이슈의 처리 상태 및 우선순위 변경 요청을 처리하고 저장한다.</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>CTX-07</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>협업</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>활동기록</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>파일 첨부 기능</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>[영업 담당자]
-- 활동 기록에 파일을 첨부하거나 첨부 파일을 다운로드할 수 있다.
-[시스템]
-- 첨부 파일을 활동기록 항목에 연결한다.</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>강성훈</t>
-        </is>
-      </c>
-      <c r="I85" s="18" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>CTX-08</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>협업</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>파일 첨부 저장/조회 API</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>[시스템]
-- 첨부 파일 업로드·저장·조회 기능을 처리한다.</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>강성훈</t>
-        </is>
-      </c>
-      <c r="I86" s="18" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>CTX-09</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>활동기록</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>FE</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>활동기록 관리 전용 페이지</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자]
 - 활동기록 관리(/activities) 페이지에서 전체 활동기록 목록을 테이블로 조회한다.
@@ -4738,49 +4541,49 @@
 - 활동기록 관련 목록은 수주건 기준으로 식별할 수 있도록 제공한다.</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I87" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>CTX-10</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>CTX-08</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>활동기록</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>활동기록 등록/수정 전용 폼</t>
         </is>
       </c>
-      <c r="F88" s="12" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - 활동기록 관리 페이지 또는 거래처 허브에서 '기록 등록' 버튼을 클릭하면 등록 폼이 표시된다.
@@ -4790,49 +4593,49 @@
 - 수주건 검색 시 선택 결과를 PO 입력값으로 반영할 수 있다.</t>
         </is>
       </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>CTX-11</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>CTX-09</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>컨택 리스트 전용 페이지</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자] 
 - 컨택 리스트(/contacts) 페이지에서 전체 바이어(연락처) 목록을 테이블로 조회한다.
@@ -4841,64 +4644,64 @@
 - 동일한 거래처 입력 방식은 연락처 등록 화면에도 적용한다.</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  인수인계</t>
         </is>
       </c>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="15" t="n"/>
-      <c r="D90" s="15" t="n"/>
-      <c r="E90" s="15" t="n"/>
-      <c r="F90" s="15" t="n"/>
-      <c r="G90" s="15" t="n"/>
-      <c r="H90" s="15" t="n"/>
-      <c r="I90" s="16" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="B86" s="15" t="n"/>
+      <c r="C86" s="15" t="n"/>
+      <c r="D86" s="15" t="n"/>
+      <c r="E86" s="15" t="n"/>
+      <c r="F86" s="15" t="n"/>
+      <c r="G86" s="15" t="n"/>
+      <c r="H86" s="15" t="n"/>
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>PKG-01</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>활동기록 패키지 생성 요청 UI</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자]
 - 거래처별 정보 페이지 상단 또는 전용 패키지 페이지(/package)의 생성 버튼을 클릭하면 생성 범위 선택 화면(기간·유형·거래건)이 나타난다.
@@ -4909,49 +4712,49 @@
 - 생성 요청 시 진행 상태를 표시하며, 완료 후 PDF 미리보기 화면으로 이동.</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>PKG-02</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>활동기록 데이터 취합/생성 API</t>
         </is>
       </c>
-      <c r="F92" s="12" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
         <is>
           <t>[시스템]
 - 사용자의 요청(기간·유형·거래건)에 따라 거래처별 정보 페이지에 누적된 데이터를 자동 취합하여 활동기록 패키지 PDF를 생성하고 저장한다.
@@ -4960,98 +4763,98 @@
 - 결재란(담당/팀장/임원) 포함.</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>PKG-03</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>Document Service</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>활동기록 PDF 이력 기록(선택)</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>[시스템]
 - 생성된 활동기록 패키지 PDF를 문서 이력에 기록한다.
 - 거래처 ID와 연결하여 추적 가능하도록 저장한다.</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>PKG-04</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E94" s="11" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>활동기록 이력 조회 UI</t>
         </is>
       </c>
-      <c r="F94" s="12" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자]
 - 활동기록 패키지 이력 목록에서 기존에 생성된 패키지를 조회하고 재다운로드한다.
@@ -5060,161 +4863,161 @@
 - 목록에 생성일시, 생성 범위(기간), 상태를 표시한다.</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H90" s="10" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I94" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>PKG-05</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>활동기록 이력 조회 API</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>[시스템] 
 - 활동기록 패키지 이력을 조회하고 PDF 다운로드 링크를 제공한다.</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>강성훈</t>
         </is>
       </c>
-      <c r="I95" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  메일/알림</t>
         </is>
       </c>
-      <c r="B96" s="15" t="n"/>
-      <c r="C96" s="15" t="n"/>
-      <c r="D96" s="15" t="n"/>
-      <c r="E96" s="15" t="n"/>
-      <c r="F96" s="15" t="n"/>
-      <c r="G96" s="15" t="n"/>
-      <c r="H96" s="15" t="n"/>
-      <c r="I96" s="16" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="B92" s="15" t="n"/>
+      <c r="C92" s="15" t="n"/>
+      <c r="D92" s="15" t="n"/>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="15" t="n"/>
+      <c r="G92" s="15" t="n"/>
+      <c r="H92" s="15" t="n"/>
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>NTF-01</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>메일 발송 API(SMTP)</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>[시스템]
 - 선택된 템플릿으로 메일 본문을 구성하고 첨부 파일을 포함하여 발송한다.
 - 발송 이력을 저장하고, 실패 시 재시도 정책에 따라 처리한다.</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I97" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>NTF-02</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E98" s="11" t="inlineStr">
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>거래처별 메일 이력 조회</t>
         </is>
       </c>
-      <c r="F98" s="12" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>[영업 담당자]
 - 사이드바의 활동 기록/메일 이력 탭에서 해당 거래처로 발송된 메일 목록을 조회한다.
@@ -5226,196 +5029,97 @@
 - 전체 거래처의 메일 이력을 조회할 수 있다.</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
+      <c r="H94" s="10" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>NTF-03</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>메일 이력 조회 API</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>[시스템]
 - 거래처별 메일 이력을 페이징 조회하고, 첨부 파일 다운로드 링크를 포함하여 반환한다.</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>NTF-04</t>
         </is>
       </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>메일</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>시스템 알림 발송(내부)</t>
-        </is>
-      </c>
-      <c r="F100" s="12" t="inlineStr">
-        <is>
-          <t>[시스템]
-- 담당자 변경, 출하 상태 변경 등 주요 이벤트 발생 시 관련 사용자에게 시스템 내부 알림을 발송한다.</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>정진호</t>
-        </is>
-      </c>
-      <c r="I100" s="18" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>NTF-05</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>알림 목록 UI</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>[사용자(공통)] 
-- 알림 아이콘을 클릭하여 시스템 알림 목록을 확인한다.
-- 읽음/안읽음 상태를 구분하여 표시한다.
-- 헤더 알림 드롭다운으로 구현. 
-- 미읽음 건수 배지 표시.</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>정진호</t>
-        </is>
-      </c>
-      <c r="I101" s="18" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>NTF-06</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t>메일</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>Activity Service</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t>FE</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
+      <c r="E96" s="11" t="inlineStr">
         <is>
           <t>메일 이력 전용 페이지</t>
         </is>
       </c>
-      <c r="F102" s="12" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자] 
 - 메일 이력(/emails) 페이지에서 전체 메일 발송 이력을 테이블로 조회한다. 
@@ -5423,64 +5127,64 @@
 - 메일 이력 화면은 제목, 거래처, 수신자, 날짜, 이메일, 발송자, 유형 조건으로 조회할 수 있다.</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H96" s="10" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  사용자 관리자</t>
         </is>
       </c>
-      <c r="B103" s="15" t="n"/>
-      <c r="C103" s="15" t="n"/>
-      <c r="D103" s="15" t="n"/>
-      <c r="E103" s="15" t="n"/>
-      <c r="F103" s="15" t="n"/>
-      <c r="G103" s="15" t="n"/>
-      <c r="H103" s="15" t="n"/>
-      <c r="I103" s="16" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+      <c r="B97" s="15" t="n"/>
+      <c r="C97" s="15" t="n"/>
+      <c r="D97" s="15" t="n"/>
+      <c r="E97" s="15" t="n"/>
+      <c r="F97" s="15" t="n"/>
+      <c r="G97" s="15" t="n"/>
+      <c r="H97" s="15" t="n"/>
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>USR-01</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>사용자 관리 - 부서 이동 탭</t>
         </is>
       </c>
-      <c r="F104" s="8" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>[관리자] 
 - 사용자 관리 페이지의 '부서 이동' 탭에서 사용자를 선택하고, 현재 부서를 확인한 뒤, 이동할 부서와 이동 사유를 입력하여 부서 이동을 처리한다. 
@@ -5488,49 +5192,49 @@
 - 부서 변경을 저장하고, 최근 부서이동 이력을 표시한다.</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>USR-02</t>
         </is>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr">
+      <c r="E99" s="11" t="inlineStr">
         <is>
           <t>사용자 관리 - 비밀번호 초기화 탭</t>
         </is>
       </c>
-      <c r="F105" s="12" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>[관리자] 
 - 사용자 관리 페이지의 '비밀번호 초기화' 탭에서 사용자를 선택하고, 비밀번호를 초기값(1234)으로 재설정한다. 
@@ -5538,49 +5242,49 @@
 - 초기화 완료 알림을 표시한다.</t>
         </is>
       </c>
-      <c r="G105" s="10" t="inlineStr">
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>USR-03</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>사용자 관리 - 자사 정보 탭</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>[관리자] 
 - 사용자 관리 페이지의 '자사 정보' 탭에서 자사 정보를 입력한다. 
@@ -5588,64 +5292,64 @@
 - 자사 정보를 저장하고, 자사 정보 입력 완료 알림을 표시한다.</t>
         </is>
       </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>정진호</t>
         </is>
       </c>
-      <c r="I106" s="17" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  공통 추가기능</t>
         </is>
       </c>
-      <c r="B107" s="15" t="n"/>
-      <c r="C107" s="15" t="n"/>
-      <c r="D107" s="15" t="n"/>
-      <c r="E107" s="15" t="n"/>
-      <c r="F107" s="15" t="n"/>
-      <c r="G107" s="15" t="n"/>
-      <c r="H107" s="15" t="n"/>
-      <c r="I107" s="16" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>COM-21</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B101" s="15" t="n"/>
+      <c r="C101" s="15" t="n"/>
+      <c r="D101" s="15" t="n"/>
+      <c r="E101" s="15" t="n"/>
+      <c r="F101" s="15" t="n"/>
+      <c r="G101" s="15" t="n"/>
+      <c r="H101" s="15" t="n"/>
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>COM-01</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>헤더 프로필 드롭다운</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>[사용자(공통)] 
 - 헤더의 사용자 영역 클릭 시 프로필 드롭다운이 열린다. 
@@ -5653,49 +5357,49 @@
 - '내 정보 수정' 버튼으로 이름/이메일 수정 모달을 연다.</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I108" s="13" t="inlineStr">
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>COM-22</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>COM-02</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>FE+BE</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr">
+      <c r="E103" s="11" t="inlineStr">
         <is>
           <t>내 정보 수정 (PATCH)</t>
         </is>
       </c>
-      <c r="F109" s="12" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
         <is>
           <t>[사용자(공통)] 
 - 이름, 이메일을 부분 수정할 수 있다. 
@@ -5704,49 +5408,49 @@
 - PATCH /api/users/{id}로 부분 수정을 처리한다.</t>
         </is>
       </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="G103" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I109" s="13" t="inlineStr">
+      <c r="I103" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>COM-23</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>COM-03</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>FE 공통</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>테이블 헤더 클릭 3중 토글 정렬</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>[사용자(공통)] 
 - 모든 BaseTable 헤더 클릭 시 기본→ASC→DESC→기본 3중 토글 정렬. 
@@ -5756,113 +5460,113 @@
 - column.sortable: false로 특정 컬럼 비활성화 가능.</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="G104" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I110" s="13" t="inlineStr">
+      <c r="I104" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>COM-24</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>COM-04</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>FE 공통</t>
         </is>
       </c>
-      <c r="D111" s="10" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr">
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>사용자 검색 사번·이름·이메일 통일</t>
         </is>
       </c>
-      <c r="F111" s="12" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
         <is>
           <t>[사용자(공통)] 
 - 모든 사용자 검색 필드에서 사번·이름·이메일로 검색 가능. 
 - placeholder "사번 · 이름 · 이메일로 검색" 통일.</t>
         </is>
       </c>
-      <c r="G111" s="10" t="inlineStr">
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="H105" s="10" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I111" s="13" t="inlineStr">
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  활동기록 패키지</t>
         </is>
       </c>
-      <c r="B112" s="15" t="n"/>
-      <c r="C112" s="15" t="n"/>
-      <c r="D112" s="15" t="n"/>
-      <c r="E112" s="15" t="n"/>
-      <c r="F112" s="15" t="n"/>
-      <c r="G112" s="15" t="n"/>
-      <c r="H112" s="15" t="n"/>
-      <c r="I112" s="16" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="B106" s="15" t="n"/>
+      <c r="C106" s="15" t="n"/>
+      <c r="D106" s="15" t="n"/>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="15" t="n"/>
+      <c r="G106" s="15" t="n"/>
+      <c r="H106" s="15" t="n"/>
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>ACT-01</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>활동기록 패키지 작성 화면</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자] 
 - PO 선택, 활동기록 체크, 제목/설명 입력 후 패키지를 생성한다. 
@@ -5872,49 +5576,49 @@
 - 생성된 패키지는 DB에 저장되고 대시보드에 표시된다.</t>
         </is>
       </c>
-      <c r="G113" s="6" t="inlineStr">
+      <c r="G107" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H113" s="6" t="inlineStr">
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I113" s="13" t="inlineStr">
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>ACT-02</t>
         </is>
       </c>
-      <c r="B114" s="10" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D114" s="10" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="E108" s="11" t="inlineStr">
         <is>
           <t>대시보드 공유 패키지 목록</t>
         </is>
       </c>
-      <c r="F114" s="12" t="inlineStr">
+      <c r="F108" s="12" t="inlineStr">
         <is>
           <t>[사용자(공통)] 
 - 대시보드에 본인이 생성하거나 열람 권한이 있는 패키지 최대 5건이 표시된다. 
@@ -5922,49 +5626,49 @@
 - 생산/출하는 전체보기 링크 없음(작성 불가, 열람만).</t>
         </is>
       </c>
-      <c r="G114" s="10" t="inlineStr">
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H114" s="10" t="inlineStr">
+      <c r="H108" s="10" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I108" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>ACT-03</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>패키지 상세 모달</t>
         </is>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>[작성자] 
 - 패키지 클릭 시 상세 모달이 열린다. 
@@ -5977,49 +5681,49 @@
 - 활동기록 클릭 시 ActivityDetailModal로 상세 열기.</t>
         </is>
       </c>
-      <c r="G115" s="6" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H115" s="6" t="inlineStr">
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I115" s="13" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>ACT-04</t>
         </is>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr">
+      <c r="E110" s="11" t="inlineStr">
         <is>
           <t>활동기록 패키지 CRUD API</t>
         </is>
       </c>
-      <c r="F116" s="12" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
         <is>
           <t>[시스템] 
 - 패키지 생성/조회/수정/삭제 API 제공. 
@@ -6027,49 +5731,49 @@
 - 조회 시 creatorName, viewerNames 포함하여 반환.</t>
         </is>
       </c>
-      <c r="G116" s="10" t="inlineStr">
+      <c r="G110" s="10" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H116" s="10" t="inlineStr">
+      <c r="H110" s="10" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I116" s="19" t="inlineStr">
-        <is>
-          <t>완</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
+      <c r="I110" s="19" t="inlineStr">
+        <is>
+          <t>완</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>ACT-05</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>패키지</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Activity Service</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>패키지 수정 모드</t>
         </is>
       </c>
-      <c r="F117" s="8" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>[영업 담당자 / 관리자] 
 - URL ?edit={id}로 기존 패키지를 불러와 수정한다. 
@@ -6078,22 +5782,23 @@
 - PUT으로 수정 저장, 대시보드로 리다이렉트.</t>
         </is>
       </c>
-      <c r="G117" s="6" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="H111" s="6" t="inlineStr">
         <is>
           <t>박찬진</t>
         </is>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I111" s="13" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
+    <row r="112" ht="28" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A2:I117"/>
   <mergeCells count="12">
